--- a/2학기_프로젝트실습/요구사항 정의서_양식2.xlsx
+++ b/2학기_프로젝트실습/요구사항 정의서_양식2.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\강의\2021-1\융합프로젝트실습1\요구사항정의서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\하이테크_태섭_수업자료\python\2학기_프로젝트실습\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28395" windowHeight="12210" tabRatio="680" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28395" windowHeight="12210" tabRatio="680"/>
   </bookViews>
   <sheets>
     <sheet name="요구사항 정의서_000기능" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
   <si>
     <t>대분류</t>
   </si>
@@ -176,12 +176,193 @@
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>다운로드</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>APP실행</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용권한</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용권한</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른앱 위에서 사용하기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>알림</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈화면</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>REQ-001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈화면 노출</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>중</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른앱 위에서 사용하기 버튼</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작 버튼</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>광고</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>라이트유저_광고</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>앱구매유저</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 실행 시 광고 7일 무료이후 
+일반 앱 서비스 처럼 광고 지속발생</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>앱 결제 사용자는 광고미노출
+앱버전 구매자는 PC버전 무료가능 사용게끔
+판매금액 추후 TBD</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>중</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴바</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈/제스처/PRO/MORE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면 하단 홈/제스처/PRO/MORE 버튼
+선택 시 각 화면으로 이동 및 노출</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 권한 미허용시 팝업허용발생
+튜토리얼 선택 시 사용방법 안내 및 카메라로 연습 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른앱 위에서 사용하기 ON시 정상동작. OFF 권한요청 팝업을 띄운다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 권한 ON시 정상동작 한다. OFF 권한요청 팝업을 띄운다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>제스처 설정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>감도 설정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>민감도 설정 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>앱 제스처 설정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용중인 앱 선택</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>URL로 다운로드 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">RO </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>RO업그레이드</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -245,6 +426,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -272,7 +460,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -350,6 +538,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -362,7 +591,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -452,6 +681,48 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -758,7 +1029,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:I24"/>
+  <dimension ref="B2:I36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.5" customWidth="1"/>
@@ -787,10 +1058,10 @@
       <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="33" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="15" t="s">
@@ -810,11 +1081,17 @@
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="B4" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>60</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>8</v>
       </c>
@@ -823,141 +1100,215 @@
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+    <row r="5" spans="2:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="B5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="32"/>
+      <c r="F5" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+    <row r="6" spans="2:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="32"/>
+      <c r="F6" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+    <row r="7" spans="2:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="B7" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="32"/>
+      <c r="F7" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="B8" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="32"/>
+      <c r="F8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="32"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="1"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="32"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+    <row r="11" spans="2:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="B11" s="31"/>
+      <c r="C11" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="43" t="s">
+        <v>52</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="5"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="32"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
+      <c r="E18" s="1"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -965,28 +1316,28 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="3"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
+      <c r="C20" s="8"/>
       <c r="D20" s="4"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="4"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="3"/>
       <c r="E21" s="1"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -995,33 +1346,169 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
+      <c r="C22" s="7"/>
       <c r="D22" s="4"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="1"/>
+      <c r="C23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="F23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="1"/>
+      <c r="C24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="F24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B27" s="8"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B28" s="8"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="8"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B34" s="8"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
